--- a/data/trans_bre/POLIPATOLOGIA_Lim_2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_Lim_2-Provincia-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,59; 22,58</t>
+          <t>8,04; 22,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,68; 24,12</t>
+          <t>10,56; 24,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 14,77</t>
+          <t>2,97; 14,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48,21; 196,95</t>
+          <t>46,91; 190,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>49,96; 216,56</t>
+          <t>59,36; 217,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,0; 119,32</t>
+          <t>15,09; 116,0</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,95; 17,42</t>
+          <t>5,9; 17,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,04; 18,26</t>
+          <t>8,52; 18,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,34; 20,77</t>
+          <t>11,81; 21,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,69; 116,54</t>
+          <t>27,15; 110,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,99; 161,11</t>
+          <t>53,56; 167,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,02; 172,47</t>
+          <t>68,16; 185,97</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 12,5</t>
+          <t>-1,26; 12,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,27; 16,78</t>
+          <t>5,74; 17,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 15,06</t>
+          <t>3,45; 14,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 73,01</t>
+          <t>-5,51; 69,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,58; 171,62</t>
+          <t>39,82; 187,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,63; 75,09</t>
+          <t>12,45; 74,6</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,84; 23,28</t>
+          <t>10,6; 22,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,56; 21,54</t>
+          <t>8,16; 20,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 10,93</t>
+          <t>-9,07; 11,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61,44; 198,2</t>
+          <t>58,07; 184,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,54; 155,48</t>
+          <t>39,95; 145,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,17; 47,62</t>
+          <t>-32,54; 48,92</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,48; 34,05</t>
+          <t>16,79; 35,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 21,97</t>
+          <t>6,03; 21,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 16,36</t>
+          <t>-2,46; 16,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57,64; 196,44</t>
+          <t>62,41; 205,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,11; 187,31</t>
+          <t>27,47; 179,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 143,17</t>
+          <t>-13,94; 150,04</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,83; 17,99</t>
+          <t>2,91; 17,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,24; 16,02</t>
+          <t>0,49; 15,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,48; 18,45</t>
+          <t>5,45; 18,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,76; 91,07</t>
+          <t>10,26; 90,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,07; 106,09</t>
+          <t>2,09; 102,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,3; 84,29</t>
+          <t>19,32; 85,48</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,15; 16,52</t>
+          <t>7,34; 16,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 11,48</t>
+          <t>2,59; 11,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 22,59</t>
+          <t>-7,91; 22,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39,24; 120,5</t>
+          <t>40,57; 119,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,99; 94,23</t>
+          <t>15,99; 94,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 104,42</t>
+          <t>-31,16; 102,41</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,33; 13,5</t>
+          <t>5,23; 12,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,59; 12,66</t>
+          <t>4,17; 12,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,26; 23,78</t>
+          <t>12,28; 23,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34,28; 112,14</t>
+          <t>32,22; 106,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,04; 90,4</t>
+          <t>22,36; 86,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>91,85; 505,48</t>
+          <t>95,36; 454,59</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,24; 14,28</t>
+          <t>10,23; 14,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,98; 12,76</t>
+          <t>8,87; 12,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,28; 16,01</t>
+          <t>7,17; 15,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56,77; 87,87</t>
+          <t>56,82; 88,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>56,81; 89,65</t>
+          <t>55,23; 91,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>43,15; 110,98</t>
+          <t>41,82; 109,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/POLIPATOLOGIA_Lim_2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_Lim_2-Provincia-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,2</t>
+          <t>8,78</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>56,24%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,04; 22,35</t>
+          <t>8,26; 21,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,56; 24,64</t>
+          <t>10,18; 24,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 14,68</t>
+          <t>3,55; 13,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46,91; 190,3</t>
+          <t>44,74; 188,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>59,36; 217,33</t>
+          <t>55,86; 225,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,09; 116,0</t>
+          <t>18,17; 109,01</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16,58</t>
+          <t>16,29</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>116,18%</t>
+          <t>113,12%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,9; 17,59</t>
+          <t>5,99; 17,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,52; 18,64</t>
+          <t>8,19; 18,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,81; 21,54</t>
+          <t>10,97; 20,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,15; 110,98</t>
+          <t>27,66; 118,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>53,56; 167,2</t>
+          <t>50,22; 162,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,16; 185,97</t>
+          <t>66,32; 176,75</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9,55</t>
+          <t>9,68</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,73%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 12,3</t>
+          <t>-1,58; 12,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,74; 17,7</t>
+          <t>5,57; 17,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 14,99</t>
+          <t>3,56; 15,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 69,87</t>
+          <t>-5,95; 72,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,82; 187,44</t>
+          <t>34,89; 184,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,45; 74,6</t>
+          <t>12,46; 75,04</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,03</t>
+          <t>10,06</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>42,23%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,6; 22,6</t>
+          <t>10,77; 22,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,16; 20,34</t>
+          <t>8,44; 21,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 11,14</t>
+          <t>3,21; 17,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58,07; 184,25</t>
+          <t>57,56; 183,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>39,95; 145,22</t>
+          <t>42,66; 154,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,54; 48,92</t>
+          <t>10,61; 89,14</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,14</t>
+          <t>13,94</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>109,37%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,79; 35,79</t>
+          <t>15,86; 33,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,03; 21,59</t>
+          <t>5,39; 21,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 16,89</t>
+          <t>8,18; 19,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62,41; 205,29</t>
+          <t>56,59; 188,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,47; 179,75</t>
+          <t>26,38; 179,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 150,04</t>
+          <t>50,02; 195,13</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11,9</t>
+          <t>12,25</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>49,24%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,91; 17,66</t>
+          <t>2,68; 17,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,49; 15,37</t>
+          <t>1,44; 15,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,45; 18,49</t>
+          <t>6,43; 19,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,26; 90,72</t>
+          <t>9,3; 90,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 102,48</t>
+          <t>4,7; 103,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,32; 85,48</t>
+          <t>22,89; 88,57</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,63</t>
+          <t>21,13</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,34; 16,03</t>
+          <t>6,69; 16,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,59; 11,33</t>
+          <t>2,66; 11,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 22,48</t>
+          <t>16,13; 25,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40,57; 119,78</t>
+          <t>38,0; 122,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,99; 94,07</t>
+          <t>16,51; 96,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,16; 102,41</t>
+          <t>64,87; 132,3</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16,83</t>
+          <t>12,93</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>180,71%</t>
+          <t>105,65%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,23; 12,98</t>
+          <t>5,55; 13,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,17; 12,27</t>
+          <t>4,36; 11,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,28; 23,32</t>
+          <t>9,82; 16,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32,22; 106,12</t>
+          <t>35,69; 111,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,36; 86,92</t>
+          <t>23,04; 86,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>95,36; 454,59</t>
+          <t>68,77; 154,4</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12,42</t>
+          <t>14,22</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>78,37%</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,23; 14,16</t>
+          <t>10,12; 14,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,87; 12,86</t>
+          <t>8,64; 12,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,17; 15,97</t>
+          <t>12,39; 16,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56,82; 88,56</t>
+          <t>55,85; 88,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>55,23; 91,31</t>
+          <t>54,63; 89,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>41,82; 109,93</t>
+          <t>64,79; 95,08</t>
         </is>
       </c>
     </row>
